--- a/02_TRAVAIL/Lot6f_CoutComplet_Menages/MASTER_CALC_CoutComplet_Menages.xlsx
+++ b/02_TRAVAIL/Lot6f_CoutComplet_Menages/MASTER_CALC_CoutComplet_Menages.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,95 +449,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>proprietaire_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>type_logement_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>intervenant_id</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nom_intervenant</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>type_intervenant</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>nb_menages</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>cout_standard_total</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>cout_direct_total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>quote_part_local</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>quote_part_courses</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>quote_part_lavage</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>quote_part_consommables</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>quote_part_autres_charges_menage</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cout_complet_total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cout_complet_unitaire</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ecart_vs_standard_total</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>statut_ecart</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>statut_controle</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>code_controle</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
@@ -561,35 +566,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>29</v>
       </c>
       <c r="J2" t="n">
         <v>29</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -604,26 +611,29 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>29</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -643,35 +653,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>145</v>
       </c>
       <c r="J3" t="n">
         <v>145</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -686,26 +698,29 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>145</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>29</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -725,35 +740,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>290</v>
       </c>
       <c r="J4" t="n">
         <v>290</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -768,26 +785,29 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>290</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>29</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -807,35 +827,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TYPE_003</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>440</v>
       </c>
       <c r="J5" t="n">
         <v>440</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -850,26 +872,29 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>440</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>55</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -889,35 +914,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>58</v>
       </c>
       <c r="J6" t="n">
         <v>58</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -932,26 +959,29 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>58</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>29</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -971,35 +1001,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>PROP_0007</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TYPE_002</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>312</v>
       </c>
       <c r="J7" t="n">
         <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1014,26 +1046,29 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>312</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>39</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1053,35 +1088,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>PROP_0003</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>TYPE_003</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>55</v>
       </c>
       <c r="J8" t="n">
         <v>55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1096,26 +1133,29 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>55</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1135,35 +1175,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>PROP_0012</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TYPE_003</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>INT_0004</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Aissata</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>110</v>
       </c>
       <c r="J9" t="n">
         <v>110</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1178,26 +1220,29 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>110</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>55</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1217,36 +1262,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>PROP_0002</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>TYPE_004</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>INT_0003</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Mounir</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>414</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>390</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -1260,26 +1307,29 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>390</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>65</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>24</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1299,36 +1349,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>PROP_0009</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TYPE_003</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>INT_0003</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Mounir</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>10</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>550</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>520</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -1342,26 +1394,29 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>520</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>52</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>30</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1381,36 +1436,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>PROP_0006</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>INT_0003</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Mounir</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>EXTERNE</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>29</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>32</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -1424,26 +1481,29 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>32</v>
       </c>
       <c r="R12" t="n">
+        <v>32</v>
+      </c>
+      <c r="S12" t="n">
         <v>-3</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1463,69 +1523,74 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>PROP_0011</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>INT_0002</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Kheira</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>INTERNE</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>116</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>110</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>5.48</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>40</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>155.48</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>38.87</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-39.48</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1545,69 +1610,74 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>PROP_0001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>INT_0002</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Kheira</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>INTERNE</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>9</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>261</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>310</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>12.33</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>90</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>412.33</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>45.81</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>-151.33</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1627,69 +1697,74 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>PROP_0005</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>INT_0002</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Kheira</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>INTERNE</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>145</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>160</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>6.85</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>60</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>226.85</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>45.37</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-81.84999999999999</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1709,69 +1784,74 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>PROP_0010</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TYPE_001</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>INT_0001</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Imène</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>INTERNE</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>261</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>210</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>12.33</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>72</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>294.33</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>32.7</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>-33.33</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1791,69 +1871,74 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>PROP_0008</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TYPE_003</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>INT_0001</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Imène</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>INTERNE</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>275</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>175</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>13</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>45</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>233</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>46.6</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>42</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/02_TRAVAIL/Lot6f_CoutComplet_Menages/MASTER_CALC_CoutComplet_Menages.xlsx
+++ b/02_TRAVAIL/Lot6f_CoutComplet_Menages/MASTER_CALC_CoutComplet_Menages.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,20 +529,25 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>ecart_unitaire</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>statut_ecart</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>statut_controle</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>code_controle</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>commentaire</t>
         </is>
@@ -622,18 +627,21 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,18 +717,21 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -796,18 +807,21 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -883,18 +897,21 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -970,18 +987,21 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1057,18 +1077,21 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1144,18 +1167,21 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1231,18 +1257,21 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>EQUILIBRE</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1318,18 +1347,21 @@
       <c r="S10" t="n">
         <v>24</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1405,18 +1437,21 @@
       <c r="S11" t="n">
         <v>30</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1492,18 +1527,21 @@
       <c r="S12" t="n">
         <v>-3</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1579,18 +1617,21 @@
       <c r="S13" t="n">
         <v>-39.48</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" t="n">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1666,18 +1707,21 @@
       <c r="S14" t="n">
         <v>-151.33</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T14" t="n">
+        <v>-16.81</v>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1753,18 +1797,21 @@
       <c r="S15" t="n">
         <v>-81.84999999999999</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" t="n">
+        <v>-16.37</v>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1840,18 +1887,21 @@
       <c r="S16" t="n">
         <v>-33.33</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T16" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>PERTE</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1927,18 +1977,21 @@
       <c r="S17" t="n">
         <v>42</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>GAIN</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>VALIDE</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2443,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2482,6 +2535,11 @@
           <t>ecart_total</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ecart_unitaire_moyen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2511,6 +2569,9 @@
       <c r="G2" t="n">
         <v>-151.33</v>
       </c>
+      <c r="H2" t="n">
+        <v>-16.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2540,6 +2601,9 @@
       <c r="G3" t="n">
         <v>24</v>
       </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2569,6 +2633,9 @@
       <c r="G4" t="n">
         <v>-81.84999999999999</v>
       </c>
+      <c r="H4" t="n">
+        <v>-16.37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2598,6 +2665,9 @@
       <c r="G5" t="n">
         <v>-3</v>
       </c>
+      <c r="H5" t="n">
+        <v>-0.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2627,6 +2697,9 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2656,6 +2729,9 @@
       <c r="G7" t="n">
         <v>42</v>
       </c>
+      <c r="H7" t="n">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2685,6 +2761,9 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2714,6 +2793,9 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2743,6 +2825,9 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2772,6 +2857,9 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2801,6 +2889,9 @@
       <c r="G12" t="n">
         <v>30</v>
       </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2830,6 +2921,9 @@
       <c r="G13" t="n">
         <v>-33.33</v>
       </c>
+      <c r="H13" t="n">
+        <v>-3.33</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2859,6 +2953,9 @@
       <c r="G14" t="n">
         <v>-39.48</v>
       </c>
+      <c r="H14" t="n">
+        <v>-9.869999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2886,6 +2983,9 @@
         <v>110</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>0</v>
       </c>
     </row>
